--- a/data/trans_dic/IP12_R2_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas 2023</t>
+          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,67</t>
+          <t>0,8; 7,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 10,79</t>
+          <t>0,99; 12,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 8,0</t>
+          <t>1,4; 7,63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 10,81</t>
+          <t>2,46; 10,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 7,36</t>
+          <t>1,5; 7,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,69</t>
+          <t>2,58; 7,73</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 14,91</t>
+          <t>3,28; 16,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 15,37</t>
+          <t>3,2; 14,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 12,22</t>
+          <t>4,35; 12,61</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,78</t>
+          <t>0,84; 8,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 18,16</t>
+          <t>1,34; 18,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 11,61</t>
+          <t>1,85; 12,09</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 19,31</t>
+          <t>4,19; 19,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,0</t>
+          <t>0,0; 9,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 11,43</t>
+          <t>3,04; 11,33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,33; 13,62</t>
+          <t>2,14; 13,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,82; 25,81</t>
+          <t>9,69; 24,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,44; 17,07</t>
+          <t>7,29; 17,28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 10,03</t>
+          <t>2,91; 9,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 10,86</t>
+          <t>3,58; 11,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 9,08</t>
+          <t>3,63; 8,77</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,21</t>
+          <t>0,92; 5,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,68</t>
+          <t>2,65; 8,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,78</t>
+          <t>2,23; 5,95</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,59</t>
+          <t>3,5; 6,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,95</t>
+          <t>4,43; 7,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,68</t>
+          <t>4,47; 6,67</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5261</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>586; 5502</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>786; 9721</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2135; 11653</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7431</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11867</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3115; 13634</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1910; 8952</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6577; 19662</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4491</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5218</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9710</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1914; 9350</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2151; 10046</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5451; 15812</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4716</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6821</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>590; 6070</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1045; 14123</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2747; 17920</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3514</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1447; 6851</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3980</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2286; 8522</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8973</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11719</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>989; 6348</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>5447; 13992</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>7461; 17685</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>7080</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>9963</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>17043</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>3627; 11974</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5580; 17821</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>10191; 24594</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>7887</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>10990</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1207; 6755</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>4158; 13767</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>6427; 17151</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>32551</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>45535</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>78086</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>23273; 42140</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>33747; 58792</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>63860; 95162</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12_R2_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por síntomas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,51</t>
+          <t>0,81; 8,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 12,25</t>
+          <t>1,01; 11,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,63</t>
+          <t>1,25; 7,44</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 10,75</t>
+          <t>2,53; 10,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 7,02</t>
+          <t>1,41; 7,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,73</t>
+          <t>2,68; 7,47</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 16,05</t>
+          <t>3,36; 15,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 14,96</t>
+          <t>3,39; 15,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 12,61</t>
+          <t>4,12; 12,54</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,65</t>
+          <t>0,61; 7,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 18,08</t>
+          <t>1,34; 17,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 12,09</t>
+          <t>1,89; 11,69</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 19,85</t>
+          <t>4,38; 18,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,78</t>
+          <t>0,0; 9,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 11,33</t>
+          <t>2,74; 11,78</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 13,75</t>
+          <t>2,22; 13,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,69; 24,9</t>
+          <t>9,06; 25,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,29; 17,28</t>
+          <t>7,2; 17,05</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,91; 9,62</t>
+          <t>2,77; 9,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,58; 11,42</t>
+          <t>3,28; 11,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,63; 8,77</t>
+          <t>3,96; 9,37</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,13</t>
+          <t>0,98; 5,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,78</t>
+          <t>2,72; 8,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,95</t>
+          <t>2,32; 6,14</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,33</t>
+          <t>3,68; 6,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,72</t>
+          <t>4,54; 7,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,67</t>
+          <t>4,57; 6,68</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por síntomas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>586; 5502</t>
+          <t>595; 5958</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>786; 9721</t>
+          <t>802; 8933</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2135; 11653</t>
+          <t>1908; 11362</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3115; 13634</t>
+          <t>3213; 13397</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1910; 8952</t>
+          <t>1797; 9689</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6577; 19662</t>
+          <t>6810; 18995</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1914; 9350</t>
+          <t>1959; 8898</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2151; 10046</t>
+          <t>2279; 10550</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5451; 15812</t>
+          <t>5170; 15727</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>590; 6070</t>
+          <t>429; 5272</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1045; 14123</t>
+          <t>1049; 13592</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2747; 17920</t>
+          <t>2806; 17336</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1447; 6851</t>
+          <t>1513; 6509</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3980</t>
+          <t>0; 3848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2286; 8522</t>
+          <t>2062; 8859</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>989; 6348</t>
+          <t>1026; 6458</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5447; 13992</t>
+          <t>5089; 14194</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7461; 17685</t>
+          <t>7367; 17449</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3627; 11974</t>
+          <t>3450; 11791</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5580; 17821</t>
+          <t>5123; 17740</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10191; 24594</t>
+          <t>11112; 26274</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1207; 6755</t>
+          <t>1284; 6845</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4158; 13767</t>
+          <t>4264; 13330</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6427; 17151</t>
+          <t>6682; 17709</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>23273; 42140</t>
+          <t>24459; 42378</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>33747; 58792</t>
+          <t>34598; 59646</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63860; 95162</t>
+          <t>65252; 95291</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R2_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,13</t>
+          <t>1,1; 11,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 11,26</t>
+          <t>0,94; 8,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,44</t>
+          <t>1,54; 8,61</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 10,56</t>
+          <t>1,34; 7,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,59</t>
+          <t>3,97; 13,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,47</t>
+          <t>3,23; 8,73</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 15,27</t>
+          <t>3,23; 14,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 15,71</t>
+          <t>3,04; 14,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 12,54</t>
+          <t>4,03; 11,66</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 7,52</t>
+          <t>1,13; 19,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 17,4</t>
+          <t>1,01; 10,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 11,69</t>
+          <t>1,97; 12,35</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 18,86</t>
+          <t>0,0; 9,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,45</t>
+          <t>4,22; 19,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 11,78</t>
+          <t>2,91; 11,86</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 13,99</t>
+          <t>9,52; 25,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,06; 25,26</t>
+          <t>2,44; 13,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,2; 17,05</t>
+          <t>7,19; 16,49</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 9,47</t>
+          <t>3,44; 11,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 11,37</t>
+          <t>3,15; 10,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,37</t>
+          <t>4,11; 9,64</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,2</t>
+          <t>2,53; 8,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,5</t>
+          <t>0,74; 4,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,14</t>
+          <t>1,96; 5,43</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,37</t>
+          <t>4,51; 8,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,83</t>
+          <t>3,82; 6,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,68</t>
+          <t>4,6; 6,89</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>4531</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>595; 5958</t>
+          <t>704; 7165</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>802; 8933</t>
+          <t>529; 4759</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1908; 11362</t>
+          <t>1862; 10382</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>11481</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3213; 13397</t>
+          <t>1547; 8138</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1797; 9689</t>
+          <t>3991; 13675</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6810; 18995</t>
+          <t>6998; 18880</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>8684</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1959; 8898</t>
+          <t>1918; 8900</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2279; 10550</t>
+          <t>1718; 7985</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5170; 15727</t>
+          <t>4673; 13522</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6955</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>429; 5272</t>
+          <t>812; 14108</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1049; 13592</t>
+          <t>713; 7625</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2806; 17336</t>
+          <t>2816; 17656</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4788</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1513; 6509</t>
+          <t>0; 3621</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3848</t>
+          <t>1504; 6842</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2062; 8859</t>
+          <t>2186; 8918</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>7784</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>10424</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1026; 6458</t>
+          <t>4661; 12593</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5089; 14194</t>
+          <t>1115; 6226</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7367; 17449</t>
+          <t>6812; 15621</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17043</t>
+          <t>16935</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3450; 11791</t>
+          <t>4860; 16801</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5123; 17740</t>
+          <t>3855; 12642</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11112; 26274</t>
+          <t>10857; 25449</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>7887</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>10470</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1284; 6845</t>
+          <t>4032; 13760</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4264; 13330</t>
+          <t>1042; 5827</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6682; 17709</t>
+          <t>5879; 16278</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>32551</t>
+          <t>42278</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>45535</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>78086</t>
+          <t>74268</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>24459; 42378</t>
+          <t>31638; 56786</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>34598; 59646</t>
+          <t>24045; 41922</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>65252; 95291</t>
+          <t>61127; 91555</t>
         </is>
       </c>
     </row>
